--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/DISPLAY_READY.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/DISPLAY_READY.xlsx
@@ -1,160 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyler\Desktop\GitHub\HUNT-BUILDER\processed_data\hard_data_exports\hunt_tables\2026\CLEAN_XLXS_STAGED\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3254A37D-F353-469A-A909-454FB202C348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="855" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="855" windowWidth="28800" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" r:id="rId1"/>
+    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$M$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Hunt Table'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
-  <si>
-    <t>Box Elder, Newfoundland Mtn</t>
-  </si>
-  <si>
-    <t>RS6722</t>
-  </si>
-  <si>
-    <t>Nov 14 2026 - Dec 06 2026</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>66.7</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>RS6727</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>SEX</t>
-  </si>
-  <si>
-    <t>SPECIES</t>
-  </si>
-  <si>
-    <t>O.I.L</t>
-  </si>
-  <si>
-    <t>WEAPON</t>
-  </si>
-  <si>
-    <t>2026 PERMITS</t>
-  </si>
-  <si>
-    <t>AVG DAYS</t>
-  </si>
-  <si>
-    <t>SEASON</t>
-  </si>
-  <si>
-    <t>ROCKY MTN SHEEP</t>
-  </si>
-  <si>
-    <t>ARCHERY</t>
-  </si>
-  <si>
-    <t>RAM</t>
-  </si>
-  <si>
-    <t>Fillmore,
- Oak Creek</t>
-  </si>
-  <si>
-    <t>HUNT
- CODE</t>
-  </si>
-  <si>
-    <t>HUNT
- NAME</t>
-  </si>
-  <si>
-    <t>HUNT
- TYPE</t>
-  </si>
-  <si>
-    <t>HUNT
- CLASS</t>
-  </si>
-  <si>
-    <t>SUCCESS
- %</t>
-  </si>
-  <si>
-    <t>HARVEST
-AVG AGE</t>
-  </si>
-  <si>
-    <t>HUNTERS
- AFIELD</t>
-  </si>
-  <si>
-    <t>2025
-HARVEST</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -216,38 +111,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FF2D1900"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -535,157 +417,258 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="1" customWidth="1"/>
-    <col min="2" max="10" width="10.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" customWidth="1"/>
-    <col min="12" max="13" width="10.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" customWidth="1"/>
+    <col width="12.5703125" customWidth="1" style="1" min="1" max="1"/>
+    <col width="10.7109375" customWidth="1" style="1" min="2" max="10"/>
+    <col width="11.7109375" customWidth="1" style="1" min="11" max="11"/>
+    <col width="10.7109375" customWidth="1" style="1" min="12" max="13"/>
+    <col width="12.5703125" customWidth="1" style="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>26</v>
+    <row r="1" ht="39.95" customHeight="1" thickBot="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>HUNT
+ NAME</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>HUNT
+ CODE</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>SPECIES</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>SEX</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>HUNT
+ TYPE</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>WEAPON</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>HUNT
+ CLASS</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>SEASON</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>2026 PERMITS</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>2025
+HARVEST</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>SUCCESS
+ %</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>HARVEST
+AVG AGE</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>AVG DAYS</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>HUNTERS
+ AFIELD</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>3</v>
-      </c>
+    <row r="2" ht="39.95" customHeight="1" thickBot="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Box Elder, Newfoundland Mtn</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>RS6722</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>ROCKY MTN SHEEP</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>O.I.L</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>ARCHERY</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Nov 14 2026 - Dec 06 2026</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
-    <row r="3" spans="1:14" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>3</v>
-      </c>
+    <row r="3" ht="39.95" customHeight="1" thickBot="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Fillmore,
+ Oak Creek</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>RS6727</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ROCKY MTN SHEEP</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>O.I.L</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>ARCHERY</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Nov 14 2026 - Dec 06 2026</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
-    <row r="17" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="30" customHeight="1"/>
+    <row r="18" ht="30" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:M3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M3"/>
   <printOptions verticalCentered="1"/>
   <pageMargins left="0.1" right="0.1" top="2" bottom="0.25" header="0" footer="0"/>
-  <pageSetup paperSize="5" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="5" scale="68" fitToHeight="0"/>
   <headerFooter>
-    <oddHeader>&amp;L
-&amp;G&amp;C
-&amp;16 &amp;18 2026 ROCKY 
-MTN SHEEP&amp;R&amp;P</oddHeader>
+    <oddHeader>&amp;L_x000a_&amp;G&amp;C&amp;18 _x000a_2026 ROCKY _x000a_MTN SHEEP&amp;R&amp;P</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
-  <legacyDrawingHF r:id="rId2"/>
 </worksheet>
 </file>